--- a/data/birthdays.xlsx
+++ b/data/birthdays.xlsx
@@ -1,42 +1,150 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amitkumar/Downloads/github-actions-birthday-slack/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2504427C-7026-FB4F-991C-4508C332FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Birthdays" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Birthdays" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Birthday</t>
+  </si>
+  <si>
+    <t>SlackUserId</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>1995-09-02</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>1997-09-15</t>
+  </si>
+  <si>
+    <t>U0987654321</t>
+  </si>
+  <si>
+    <t>Priya</t>
+  </si>
+  <si>
+    <t>1996-09-25</t>
+  </si>
+  <si>
+    <t>U0234567890</t>
+  </si>
+  <si>
+    <t>Neha</t>
+  </si>
+  <si>
+    <t>1998-10-05</t>
+  </si>
+  <si>
+    <t>U0345678901</t>
+  </si>
+  <si>
+    <t>Rohit</t>
+  </si>
+  <si>
+    <t>1994-11-20</t>
+  </si>
+  <si>
+    <t>U0456789012</t>
+  </si>
+  <si>
+    <t>Ankit</t>
+  </si>
+  <si>
+    <t>1999-12-10</t>
+  </si>
+  <si>
+    <t>U0567890123</t>
+  </si>
+  <si>
+    <t>Pooja</t>
+  </si>
+  <si>
+    <t>1997-12-25</t>
+  </si>
+  <si>
+    <t>U0678901234</t>
+  </si>
+  <si>
+    <t>Vikas</t>
+  </si>
+  <si>
+    <t>1995-01-15</t>
+  </si>
+  <si>
+    <t>U0789012345</t>
+  </si>
+  <si>
+    <t>Sneha</t>
+  </si>
+  <si>
+    <t>1998-02-28</t>
+  </si>
+  <si>
+    <t>U0890123456</t>
+  </si>
+  <si>
+    <t>Karan</t>
+  </si>
+  <si>
+    <t>1996-03-12</t>
+  </si>
+  <si>
+    <t>U0901234567</t>
+  </si>
+  <si>
+    <t>U0BU6RASK1U</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -55,81 +163,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -417,204 +466,134 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Birthday</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SlackUserId</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Amit</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1995-09-02</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>U0123456789</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Rahul</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1997-09-15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>U0987654321</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Priya</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1996-09-25</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>U0234567890</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Neha</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1998-10-05</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>U0345678901</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Rohit</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1994-11-20</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>U0456789012</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ankit</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1999-12-10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>U0567890123</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Pooja</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1997-12-25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>U0678901234</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Vikas</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1995-01-15</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>U0789012345</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sneha</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1998-02-28</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>U0890123456</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Karan</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1996-03-12</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>U0901234567</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/birthdays.xlsx
+++ b/data/birthdays.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amitkumar/Downloads/github-actions-birthday-slack/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2504427C-7026-FB4F-991C-4508C332FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303D8A13-833D-CC46-8B75-3599E6827EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>Amit</t>
-  </si>
-  <si>
-    <t>1995-09-02</t>
   </si>
   <si>
     <t>Rahul</t>
@@ -162,9 +159,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -490,110 +488,110 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2" s="2">
+        <v>34943</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/data/birthdays.xlsx
+++ b/data/birthdays.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amitkumar/Downloads/github-actions-birthday-slack/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303D8A13-833D-CC46-8B75-3599E6827EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB15FF89-F225-B345-B1BA-085435819D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="600" windowWidth="18200" windowHeight="8500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Birthdays" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -34,13 +34,13 @@
     <t>Amit</t>
   </si>
   <si>
+    <t>U0BU6RASK1U</t>
+  </si>
+  <si>
     <t>Rahul</t>
   </si>
   <si>
-    <t>1997-09-15</t>
-  </si>
-  <si>
-    <t>U0987654321</t>
+    <t>1997-09-1</t>
   </si>
   <si>
     <t>Priya</t>
@@ -115,14 +115,14 @@
     <t>U0901234567</t>
   </si>
   <si>
-    <t>U0BU6RASK1U</t>
+    <t xml:space="preserve"> 1997-09-1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,10 +133,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -147,7 +152,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -159,10 +171,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -255,6 +277,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -289,6 +312,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -312,7 +336,6 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
@@ -323,31 +346,31 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -369,7 +392,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -427,7 +450,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -440,13 +463,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -465,129 +487,132 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2">
-        <v>34943</v>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
@@ -595,6 +620,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/birthdays.xlsx
+++ b/data/birthdays.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amitkumar/Downloads/github-actions-birthday-slack/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB15FF89-F225-B345-B1BA-085435819D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08FC48A-D8FB-5E49-8C87-9C22037378C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="600" windowWidth="18200" windowHeight="8500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Rahul</t>
   </si>
   <si>
-    <t>1997-09-1</t>
-  </si>
-  <si>
     <t>Priya</t>
   </si>
   <si>
@@ -115,7 +112,7 @@
     <t>U0901234567</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1997-09-1</t>
+    <t xml:space="preserve"> 1997-09-2</t>
   </si>
 </sst>
 </file>
@@ -514,7 +511,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -525,7 +522,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -533,90 +530,90 @@
     </row>
     <row r="4" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" t="s">
         <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" t="s">
         <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/data/birthdays.xlsx
+++ b/data/birthdays.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amitkumar/Downloads/github-actions-birthday-slack/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08FC48A-D8FB-5E49-8C87-9C22037378C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F109B3-4606-2745-8DC5-C2FD325D3463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="600" windowWidth="18200" windowHeight="8500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/birthdays.xlsx
+++ b/data/birthdays.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amitkumar/Downloads/github-actions-birthday-slack/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F109B3-4606-2745-8DC5-C2FD325D3463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{030DB31F-7338-4442-87ED-32BBE6A6B0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="600" windowWidth="18200" windowHeight="8500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10600" yWindow="3560" windowWidth="18200" windowHeight="8500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Birthdays" sheetId="1" r:id="rId1"/>
@@ -82,9 +82,6 @@
     <t>1997-12-25</t>
   </si>
   <si>
-    <t>U0678901234</t>
-  </si>
-  <si>
     <t>Vikas</t>
   </si>
   <si>
@@ -109,10 +106,13 @@
     <t>1996-03-12</t>
   </si>
   <si>
-    <t>U0901234567</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 1997-09-2</t>
+  </si>
+  <si>
+    <t>U09012345675</t>
+  </si>
+  <si>
+    <t>U067890123422</t>
   </si>
 </sst>
 </file>
@@ -511,7 +511,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -522,7 +522,7 @@
         <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -580,37 +580,37 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" t="s">
         <v>22</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" t="s">
         <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>29</v>
